--- a/per-stock/SNOW/financials.xlsx
+++ b/per-stock/SNOW/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54437380096</v>
+        <v>80511713280</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53085974528</v>
+        <v>80328810496</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64.97038000000001</v>
+        <v>86.54458</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.62212</v>
+        <v>15.997327</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -608,7 +617,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.67169</v>
+        <v>0.67144996</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -623,7 +632,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.33236998</v>
+        <v>-0.22173999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -638,7 +647,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.28429002</v>
+        <v>-0.23786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -653,7 +662,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.53908</v>
+        <v>-0.54869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -668,7 +677,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.301</v>
+        <v>0.335</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -683,7 +692,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4029686016</v>
+        <v>2954998016</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -698,7 +707,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2741114112</v>
+        <v>2772094976</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1587485568</v>
+        <v>1166601000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -728,7 +737,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>345700000</v>
+        <v>346600000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>157.47</v>
+        <v>232.29</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,468 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D48</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C48</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B48</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B48:E48)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D46</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C46</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B46</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B46:E46)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D39</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C39</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B39</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B39:E39)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B5:E5)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1746,7 +2217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1771,27 +2242,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
         </is>
       </c>
     </row>
@@ -1802,19 +2273,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-37992</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-9750000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-53550</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-6233850</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>57658.311494</v>
       </c>
     </row>
     <row r="3">
@@ -1824,19 +2295,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.21</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.013122</v>
       </c>
     </row>
     <row r="4">
@@ -1846,19 +2317,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-217477000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-216521000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-227713000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-235377000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-343663000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-282249000</v>
       </c>
     </row>
     <row r="5">
@@ -1868,19 +2339,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-9498000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-24375000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-255000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-5580000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-29685000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>4394000</v>
       </c>
     </row>
     <row r="6">
@@ -1890,19 +2361,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-9498000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-24375000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-255000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-5580000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-29685000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>4394000</v>
       </c>
     </row>
     <row r="7">
@@ -1912,19 +2383,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-295571000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-309550000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-293957000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-298017000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-430092000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>-327474000</v>
       </c>
     </row>
     <row r="8">
@@ -1934,19 +2405,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>67605000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>58924000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>57878000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>54837000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>48804000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>50130000</v>
       </c>
     </row>
     <row r="9">
@@ -1956,19 +2427,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>464500000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>426331000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>390873000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>371815000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>348786000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>333184000</v>
       </c>
     </row>
     <row r="10">
@@ -1978,19 +2449,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-226975000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-240896000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-227968000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-240957000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-373348000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>-277855000</v>
       </c>
     </row>
     <row r="11">
@@ -2000,19 +2471,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-294580000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-299820000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-285846000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-295794000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-422152000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>-327985000</v>
       </c>
     </row>
     <row r="12">
@@ -2022,19 +2493,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>39065000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>40367000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>43406000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>47393000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>51092000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>54240000</v>
       </c>
     </row>
     <row r="13">
@@ -2044,19 +2515,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>2080000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>2078000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>2075000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>2074000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>2071000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>2070000</v>
       </c>
     </row>
     <row r="14">
@@ -2066,19 +2537,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>41145000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>42445000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>45481000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>49467000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>53163000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>56310000</v>
       </c>
     </row>
     <row r="15">
@@ -2088,19 +2559,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-286110992</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-294925000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-293755550</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-292437000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-406640850</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>-331810341.688506</v>
       </c>
     </row>
     <row r="16">
@@ -2110,19 +2581,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-295571000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-309550000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-293957000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-298017000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-430092000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>-327474000</v>
       </c>
     </row>
     <row r="17">
@@ -2132,19 +2603,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>1717105000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>1602153000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>1542382000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>1485245000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>1489331000</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>1373448000</v>
       </c>
     </row>
     <row r="18">
@@ -2154,19 +2625,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-326154000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-318159000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-329473000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-340276000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-447257000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>-386678000</v>
       </c>
     </row>
     <row r="19">
@@ -2176,19 +2647,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>345391000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>342295000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>339648000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>335215000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>332657000</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>331432000</v>
       </c>
     </row>
     <row r="20">
@@ -2198,19 +2669,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>345391000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>342295000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>339648000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>335215000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>332657000</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>331432000</v>
       </c>
     </row>
     <row r="21">
@@ -2220,19 +2691,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-0.9</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-0.87</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-0.89</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-1.29</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>-0.99</v>
       </c>
     </row>
     <row r="22">
@@ -2242,19 +2713,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-0.9</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-0.87</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-0.89</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-1.29</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>-0.99</v>
       </c>
     </row>
     <row r="23">
@@ -2264,19 +2735,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-295571000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-309550000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-293957000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-298017000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-430092000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>-327474000</v>
       </c>
     </row>
     <row r="24">
@@ -2286,19 +2757,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-295571000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-309550000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-293957000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-298017000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-430092000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>-327474000</v>
       </c>
     </row>
     <row r="25">
@@ -2308,19 +2779,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-295571000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-309550000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-293957000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-298017000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-430092000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>-327474000</v>
       </c>
     </row>
     <row r="26">
@@ -2333,16 +2804,16 @@
         <v>0</v>
       </c>
       <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>-2354000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-87000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-140000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-1750000</v>
       </c>
     </row>
     <row r="27">
@@ -2352,19 +2823,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-295571000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-309550000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-291603000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-297930000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-429952000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>-325724000</v>
       </c>
     </row>
     <row r="28">
@@ -2374,19 +2845,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-295571000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-309550000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-291603000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-297930000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-429952000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>-325724000</v>
       </c>
     </row>
     <row r="29">
@@ -2396,19 +2867,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-1089000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>7652000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>3682000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>62000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>5729000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-4331000</v>
       </c>
     </row>
     <row r="30">
@@ -2418,19 +2889,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-296660000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-301898000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-287921000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-297868000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-424223000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>-330055000</v>
       </c>
     </row>
     <row r="31">
@@ -2440,19 +2911,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-9571000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-24106000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-1854000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-4985000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-28058000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>2383000</v>
       </c>
     </row>
     <row r="32">
@@ -2462,19 +2933,19 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-73000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>269000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-1599000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>595000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>1627000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>-2011000</v>
       </c>
     </row>
     <row r="33">
@@ -2484,19 +2955,19 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-21831000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-500000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-26521000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2506,19 +2977,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>21831000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>26521000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2528,19 +2999,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-7498000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-2544000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>245000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-580000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-3164000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>4394000</v>
       </c>
     </row>
     <row r="36">
@@ -2550,19 +3021,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>39065000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>40367000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>43406000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>47393000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>51092000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>54240000</v>
       </c>
     </row>
     <row r="37">
@@ -2572,19 +3043,19 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>2080000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>2078000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>2075000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>2074000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>2071000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>2070000</v>
       </c>
     </row>
     <row r="38">
@@ -2594,19 +3065,19 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>41145000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>42445000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>45481000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>49467000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>53163000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>56310000</v>
       </c>
     </row>
     <row r="39">
@@ -2616,19 +3087,19 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-326154000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-318159000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-329473000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-340276000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-447257000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>-386678000</v>
       </c>
     </row>
     <row r="40">
@@ -2638,19 +3109,19 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>1252605000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>1175822000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>1151509000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>1113430000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>1140545000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>1040264000</v>
       </c>
     </row>
     <row r="41">
@@ -2660,19 +3131,19 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>534937000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>511038000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>494027000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>492003000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>472404000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>492490000</v>
       </c>
     </row>
     <row r="42">
@@ -2682,19 +3153,19 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>717668000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>664784000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>657482000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>621427000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>668141000</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>547774000</v>
       </c>
     </row>
     <row r="43">
@@ -2704,19 +3175,19 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>588952000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>551262000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>550364000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>501957000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>458554000</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>432683000</v>
       </c>
     </row>
     <row r="44">
@@ -2726,19 +3197,19 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>128716000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>113522000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>107118000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>119470000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>209587000</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>115091000</v>
       </c>
     </row>
     <row r="45">
@@ -2748,19 +3219,19 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>128716000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>113522000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>107118000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>119470000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>209587000</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>115091000</v>
       </c>
     </row>
     <row r="46">
@@ -2770,19 +3241,19 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>926451000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>857663000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>822036000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>773154000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>693288000</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>653586000</v>
       </c>
     </row>
     <row r="47">
@@ -2792,19 +3263,19 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>464500000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>426331000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>390873000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>371815000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>348786000</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>333184000</v>
       </c>
     </row>
     <row r="48">
@@ -2814,19 +3285,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>1390951000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>1283994000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>1212909000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>1144969000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>1042074000</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>986770000</v>
       </c>
     </row>
     <row r="49">
@@ -2836,19 +3307,19 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>1390951000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>1283994000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>1212909000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>1144969000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>1042074000</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>986770000</v>
       </c>
     </row>
   </sheetData>
@@ -2856,7 +3327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4318,7 +4789,1777 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>390000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>399000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>408000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>417000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>426000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>346601283</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>343918000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>342065000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>338762000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>333638697</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>346991283</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>344317000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>342473000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>339179000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>334064697</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>197188000</v>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
+        <v>336092000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>394954000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>30517000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n">
+        <v>120531000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2772095000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2741114000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2685615000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2692329000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2687763000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-109131000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>365193000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>573722000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>776331000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>957393000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>4221625000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>4203929000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>4410682000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>4648322000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>4681600000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>199816000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1320921000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1240181000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1500045000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1755430000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-109131000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>365193000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>573722000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>776331000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>957393000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>490192000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>461287000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>407866000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>416655000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>414163000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1939722000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1924102000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2132933000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2372648000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2408000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>4221625000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>4203929000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>4410682000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>4648322000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>4681600000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1939722000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1924102000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2132933000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2379589000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2414854000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>6941000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>6854000</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>6714000</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1939722000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1924102000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>2132933000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2372648000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2408000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-3639000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>3337000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>5123000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2782000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>8171000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-3639000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>3337000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>5123000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2782000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>8171000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>53261000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>54488000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>55714000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>56968000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>58153000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>-10089823000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-9494249000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-9034696000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-8512322000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-8214507000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>12086411000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>11469468000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>11218186000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>10939122000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>10672455000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>34000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>6614534000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>7208393000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>6097258000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5817138000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>5742553000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>2837243000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2786702000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2713944000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>2721056000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2712009000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>95268000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>80746000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>57653000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>55296000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>47620000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>25663000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>14440000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>10884000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>11540000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>13724000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>25663000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>14440000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>10884000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>11540000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>13724000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>2716312000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2691516000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>2645407000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2654220000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>2650665000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>434409000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>411689000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>367658000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>378546000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>377065000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>2281903000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>2279827000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>2277749000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>2275674000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2273600000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>3777291000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4421691000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>3383314000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>3096082000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>3030544000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>136177000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>126419000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>175708000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>120767000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>95716000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>2851812000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>3346997000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>2423622000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>2268387000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2309803000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2851812000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>3346997000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>2423622000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>2268387000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2309803000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>55783000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>49598000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>40208000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>38109000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>37098000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>55783000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>49598000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>40208000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>38109000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>37098000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>263671000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>373780000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>324021000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>262852000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>211781000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>469848000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>524897000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>419755000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>405967000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>376146000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>383441000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>325571000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>179721000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>168337000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>198524000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>86407000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>199326000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>240034000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>237630000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>177622000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>31345000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>53767000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>46343000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>70844000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>22359000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>55062000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>145559000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>193691000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>166786000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>155263000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>8554256000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>9132495000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>8230191000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>8196727000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>8157407000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>4577149000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3389883000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>3606696000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>3600600000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>3371433000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>412043000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>428320000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>403686000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>394594000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>369722000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>222000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>241759000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>209511000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>187206000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>182761000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>1432494000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>755013000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1041474000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1012904000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>956144000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1432494000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>755013000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1041474000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1012904000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>956144000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>1432494000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>755013000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1041474000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1012904000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>956144000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>2048853000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1558909000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1559211000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1596317000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1450607000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>511668000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>364542000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>384251000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>421339000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>394048000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1537185000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1194367000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>1174960000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>1174978000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1056559000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>461759000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>405882000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>392814000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>409579000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>412199000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>-95173000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>-126397000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>-109354000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-94727000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>-81582000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>556932000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>532279000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>502168000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>504306000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>493781000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>135589000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>133374000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>125781000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>117022000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>81135000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>11190000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>22247000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>22281000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>29663000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>72232000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>294863000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>274897000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>254641000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>262419000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>261971000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>115290000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>101761000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>99465000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>95202000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>78443000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>3977107000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>5742612000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>4623495000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>4596127000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>4785974000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>229504000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>195128000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>164319000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>232864000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>240586000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>212886000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>214058000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>167926000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>129873000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>104187000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>579719000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1303740000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>938145000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>646682000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>530517000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>579719000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1303740000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>938145000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>646682000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>530517000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>-3700000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-7800000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>-4200000</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>-4800000</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>-2800000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n">
+        <v>941845000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>654482000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>534717000</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>927605000</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>599152000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>2954998000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>4029686000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>3353105000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>3586708000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>3910684000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>870283000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1201523000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1411448000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>1705988000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>1667601000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>2084715000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>2828163000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1941657000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>1880720000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>2243083000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5524,13 +7765,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5540,6 +7781,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5550,30 +7792,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5586,21 +7833,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>232772000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>763295000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>113614000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>56920000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>183384000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>415443000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5609,21 +7857,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-300003000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-150003000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-232896000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-490638000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5631,16 +7880,17 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5649,21 +7899,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-10451000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-17859000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-23905000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-17976000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-44989000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-17282000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5672,21 +7923,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>2128678000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>2864303000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>1984631000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>1960838000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>2319408000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>2698678000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5695,21 +7947,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>2864303000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>1984631000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>1960838000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>2319408000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>2698678000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>2166238000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5718,21 +7971,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>-2824000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>4589000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>21000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>-175000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>12397000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>-5055000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5741,21 +7995,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>-732801000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>875083000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>23772000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>-358395000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>-391667000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>537495000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5764,21 +8019,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-371533000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-325308000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-361986000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-134039000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-564057000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-120118000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5787,21 +8043,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-371533000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-325308000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-361986000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-134039000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-564057000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-120118000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5810,21 +8067,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-145096000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-196140000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-192869000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-162225000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-132872000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-129792000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5833,21 +8091,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>73566000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>20835000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>63779000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>28186000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>59453000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>9674000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5856,21 +8115,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-300003000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-150003000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-232896000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-490638000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5879,21 +8139,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-300003000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-150003000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-232896000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-490638000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5901,16 +8162,17 @@
           <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5918,16 +8180,17 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5935,16 +8198,17 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5953,21 +8217,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-604491000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>419237000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>248239000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-299252000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-55983000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>224888000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5976,21 +8241,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-604491000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>419237000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>248239000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-299252000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-55983000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>224888000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5999,21 +8265,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-341583000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>451716000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>272144000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-117046000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-10994000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>256099000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6022,21 +8289,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>554864000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>501920000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>613316000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>519423000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>1001581000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>535608000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6045,21 +8313,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-896447000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-50204000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-341172000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-636469000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-1012575000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-279509000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6068,19 +8337,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-252457000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-14620000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
+      <c r="E24" s="3" t="n">
+        <v>-164230000</v>
+      </c>
       <c r="F24" s="3" t="n">
-        <v>-13180000</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>-8219000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6089,19 +8361,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-252457000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-14620000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
+      <c r="E25" s="3" t="n">
+        <v>-164230000</v>
+      </c>
       <c r="F25" s="3" t="n">
-        <v>-13180000</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>-8219000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6109,20 +8384,21 @@
           <t>Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n">
         <v>-1790000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H26" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6130,20 +8406,21 @@
           <t>Purchase Of Intangibles</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n">
         <v>-1790000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6152,21 +8429,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-10451000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-16069000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-23905000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-16665000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-44989000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-11277000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6175,21 +8453,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-10451000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-16069000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-23905000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-16665000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-44989000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-11277000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6197,9 +8476,7 @@
           <t>Capital Expenditure Reported</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" s="3" t="n"/>
       <c r="C30" s="3" t="n">
         <v>0</v>
       </c>
@@ -6210,9 +8487,12 @@
         <v>0</v>
       </c>
       <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
         <v>-6005000</v>
       </c>
-      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6221,21 +8501,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>243223000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>781154000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>137519000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>74896000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>228373000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>432725000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6244,21 +8525,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>243223000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>781154000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>137519000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>74896000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>228373000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>432725000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6267,21 +8549,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-30249000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>541244000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-80639000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-137850000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>61005000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>254821000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6290,21 +8573,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-565340000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>804255000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>54636000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-106261000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>-302474000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>570657000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6313,21 +8597,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-19207000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>15438000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-15990000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-14559000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-11838000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-13367000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6336,21 +8621,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-170464000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>130896000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>149568000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>105062000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-488000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>38305000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6359,21 +8645,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-80791000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>175491000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>120620000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>93291000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>3935000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>32174000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6382,21 +8669,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-89673000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-44595000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>28948000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>11771000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-4423000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>6131000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6405,21 +8693,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-89673000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-44595000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>28948000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>11771000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-4423000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>6131000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6428,21 +8717,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-22455000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-42001000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>19823000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-4486000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-17852000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-12606000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6451,21 +8741,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>747217000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-367344000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-288676000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-117606000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>393657000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-328168000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6474,21 +8765,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>747217000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-367344000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-288676000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-117606000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>393657000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-328168000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6497,21 +8789,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>80513000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>64805000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>44354000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>53073000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>40535000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>46477000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6520,21 +8813,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>402470000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>403592000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>412278000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>404217000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>379460000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>428119000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6543,21 +8837,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>17724000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>96000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>2131000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>106488000</v>
       </c>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6566,21 +8861,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>-2205000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>-3344000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-5100000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-5717000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-7652000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-9565000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6589,19 +8885,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>-6562000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>1108000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
+      <c r="E47" s="3" t="n">
+        <v>-3445000</v>
+      </c>
       <c r="F47" s="3" t="n">
-        <v>-7139000</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>-581000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6610,19 +8909,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>-6562000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>1108000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
+      <c r="E48" s="3" t="n">
+        <v>-3445000</v>
+      </c>
       <c r="F48" s="3" t="n">
-        <v>-7139000</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>-581000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6631,21 +8933,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>67605000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>58924000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>57878000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>54837000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>48804000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>50130000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6654,21 +8957,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>67605000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>58924000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>57878000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>54837000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>48804000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>50130000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6677,21 +8981,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>9498000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>24375000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>255000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>5580000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>29685000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>-4394000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6700,21 +9005,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>9498000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>24375000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>255000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>5580000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>29685000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>-4394000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6723,34 +9029,35 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>-295571000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>-309550000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>-291603000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>-297930000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>-429952000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>-325724000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6781,6 +9088,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FY Summary</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>'Net Debt' not found in statements — left blank</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
